--- a/A-pojat.xlsx
+++ b/A-pojat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812B7025-59A9-4042-A33D-8747002FC975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3145E2-CBEA-4F7E-87EE-3ACC24948179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1764" yWindow="732" windowWidth="21276" windowHeight="12948" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" activeTab="1" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="A 2025-2027" sheetId="10" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
   <si>
     <t>päivä</t>
   </si>
@@ -224,6 +224,15 @@
   </si>
   <si>
     <t>2026-2027</t>
+  </si>
+  <si>
+    <t>31.10.2026</t>
+  </si>
+  <si>
+    <t>Viesti/NarPa</t>
+  </si>
+  <si>
+    <t>PuMa 3</t>
   </si>
 </sst>
 </file>
@@ -866,7 +875,9 @@
   <dimension ref="A1:S27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="10.77734375" customWidth="1"/>
+    <col min="1" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" customWidth="1"/>
     <col min="6" max="6" width="16.88671875" customWidth="1"/>
     <col min="7" max="18" width="10.77734375" customWidth="1"/>
   </cols>
@@ -920,9 +931,9 @@
       </c>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="19">
-        <v>45962</v>
+    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>7</v>
@@ -930,7 +941,9 @@
       <c r="C2" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="20"/>
+      <c r="D2" s="20" t="s">
+        <v>63</v>
+      </c>
       <c r="E2" s="21"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
@@ -961,10 +974,18 @@
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="23"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="A3" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>64</v>
+      </c>
       <c r="E3" s="15"/>
       <c r="F3" s="14"/>
       <c r="G3" s="8"/>
@@ -992,10 +1013,18 @@
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
+      <c r="A4" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>40</v>
+      </c>
       <c r="E4" s="21"/>
       <c r="F4" s="20"/>
       <c r="G4" s="10"/>
